--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,13 +108,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>MedicationRequest</t>
+    <t>ServiceRequest</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
+    <t>http://hl7.org/fhir/StructureDefinition/ServiceRequest</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -240,7 +240,7 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: Mapping to NCPDP SCRIPT 10.6</t>
+    <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -249,11 +249,11 @@
     <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Prescription
-Order</t>
+    <t>Mapping: Quality Improvement and Clinical Knowledge (QUICK)</t>
+  </si>
+  <si>
+    <t>diagnostic request
+referralreferral requesttransfer of care request</t>
   </si>
   <si>
     <t>0</t>
@@ -269,26 +269,26 @@
 </t>
   </si>
   <si>
-    <t>Ordering of medication for patient or group</t>
-  </si>
-  <si>
-    <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
+    <t>A request for a service to be performed</t>
+  </si>
+  <si>
+    <t>A record of a request for service such as diagnostic investigations, treatments, or operations to be performed.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
   </si>
   <si>
     <t>Request</t>
   </si>
   <si>
-    <t>Message/Body/NewRx</t>
-  </si>
-  <si>
-    <t>CombinedMedicationRequest</t>
-  </si>
-  <si>
-    <t>MedicationRequest.id</t>
+    <t>ORC</t>
+  </si>
+  <si>
+    <t>Act[moodCode&lt;=INT]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.id</t>
   </si>
   <si>
     <t>1</t>
@@ -313,7 +313,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>MedicationRequest.meta</t>
+    <t>ServiceRequest.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -333,7 +333,7 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.implicitRules</t>
+    <t>ServiceRequest.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -352,7 +352,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>MedicationRequest.language</t>
+    <t>ServiceRequest.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -380,7 +380,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>MedicationRequest.text</t>
+    <t>ServiceRequest.text</t>
   </si>
   <si>
     <t>narrative
@@ -406,7 +406,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>MedicationRequest.contained</t>
+    <t>ServiceRequest.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -432,36 +432,83 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>MedicationRequest.extension</t>
+    <t>ServiceRequest.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:cpg-rating</t>
+  </si>
+  <si>
+    <t>cpg-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-rating}
+</t>
+  </si>
+  <si>
+    <t>CPG Rating Extension</t>
+  </si>
+  <si>
+    <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:coded-rating</t>
+  </si>
+  <si>
+    <t>coded-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSCodedRating}
+</t>
+  </si>
+  <si>
+    <t>PSS Rating Extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.extension:structured-rating</t>
+  </si>
+  <si>
+    <t>structured-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -469,176 +516,276 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier</t>
+    <t>ServiceRequest.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>External ids for this request</t>
-  </si>
-  <si>
-    <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier.</t>
+    <t>Identifiers assigned to this order</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
+  </si>
+  <si>
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
     <t>Request.identifier</t>
   </si>
   <si>
-    <t>Message/Header/PrescriberOrderNumber</t>
-  </si>
-  <si>
-    <t>.id</t>
+    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
+  </si>
+  <si>
+    <t>.identifier</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status</t>
-  </si>
-  <si>
-    <t>active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
-  </si>
-  <si>
-    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+    <t>ClinicalStatement.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
+  </si>
+  <si>
+    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Request.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Request.instantiatesUri</t>
+  </si>
+  <si>
+    <t>ServiceRequest.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+</t>
+  </si>
+  <si>
+    <t>What request fulfills</t>
+  </si>
+  <si>
+    <t>Plan/proposal/order fulfilled by this request.</t>
+  </si>
+  <si>
+    <t>Request.basedOn</t>
+  </si>
+  <si>
+    <t>ORC.8 (plus others)</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.replaces</t>
+  </si>
+  <si>
+    <t>supersedes
+priorrenewed order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest)
+</t>
+  </si>
+  <si>
+    <t>What request replaces</t>
+  </si>
+  <si>
+    <t>The request takes the place of the referenced completed or terminated request(s).</t>
+  </si>
+  <si>
+    <t>Request.replaces</t>
+  </si>
+  <si>
+    <t>Handled by message location of ORC (ORC.1=RO or RU)</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RPLC].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requisition</t>
+  </si>
+  <si>
+    <t>grouperId
+groupIdentifier</t>
+  </si>
+  <si>
+    <t>Composite Request ID</t>
+  </si>
+  <si>
+    <t>A shared identifier common to all service requests that were authorized more or less simultaneously by a single author, representing the composite or group identifier.</t>
+  </si>
+  <si>
+    <t>Requests are linked either by a "basedOn" relationship (i.e. one request is fulfilling another) or by having a common requisition. Requests that are part of the same requisition are generally treated independently from the perspective of changing their state or maintaining them after initial creation.</t>
+  </si>
+  <si>
+    <t>Some business processes need to know if multiple items were ordered as part of the same "requisition" for billing or other purposes.</t>
+  </si>
+  <si>
+    <t>Request.groupIdentifier</t>
+  </si>
+  <si>
+    <t>ORC.4</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=COMP].source[moodCode=INT].identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.status</t>
+  </si>
+  <si>
+    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>The status of the order.</t>
+  </si>
+  <si>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](http://hl7.org/fhir/R4/event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status|4.0.1</t>
+    <t>The status of a service order.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status</t>
   </si>
   <si>
-    <t>no mapping</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
+    <t>ORC.5,RF1-1</t>
+  </si>
+  <si>
+    <t>.status</t>
   </si>
   <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>MedicationRequest.statusReason</t>
+    <t>Action.currentStatus</t>
+  </si>
+  <si>
+    <t>ServiceRequest.intent</t>
+  </si>
+  <si>
+    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
+  </si>
+  <si>
+    <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
+  </si>
+  <si>
+    <t>proposal</t>
+  </si>
+  <si>
+    <t>The kind of service request.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.intent</t>
+  </si>
+  <si>
+    <t>.moodCode (nuances beyond PRP/PLAN/RQO would need to be elsewhere)</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>Captures the reason for the current state of the MedicationRequest.</t>
-  </si>
-  <si>
-    <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
+    <t>Classification of service</t>
+  </si>
+  <si>
+    <t>A code that classifies the service for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Identifies the reasons for a given status.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
-  </si>
-  <si>
-    <t>Request.statusReason</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN].reasonCOde</t>
-  </si>
-  <si>
-    <t>MedicationRequest.intent</t>
-  </si>
-  <si>
-    <t>proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
-  </si>
-  <si>
-    <t>Whether the request is a proposal, plan, or an original order.</t>
-  </si>
-  <si>
-    <t>It is expected that the type of requester will be restricted for different stages of a MedicationRequest.  For example, Proposals can be created by a patient, relatedPerson, Practitioner or Device.  Plans can be created by Practitioners, Patients, RelatedPersons and Devices.  Original orders can be created by a Practitioner only.--An instance-order is an instantiation of a request or order and may be used to populate Medication Administration Record.--This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
-  </si>
-  <si>
-    <t>proposal</t>
-  </si>
-  <si>
-    <t>The kind of medication order.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.intent</t>
-  </si>
-  <si>
-    <t>.moodCode (nuances beyond PRP/PLAN/RQO would need to be elsewhere)</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category</t>
-  </si>
-  <si>
-    <t>Type of medication usage</t>
-  </si>
-  <si>
-    <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
-  </si>
-  <si>
-    <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Directions--or --Message/Body/NewRx/MedicationPrescribed/StructuredSIG</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.priority</t>
+    <t>Classification of the requested service.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+  </si>
+  <si>
+    <t>RF1-5</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="INT"].code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.priority</t>
   </si>
   <si>
     <t>routine | urgent | asap | stat</t>
   </si>
   <si>
-    <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
+    <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
@@ -650,849 +797,616 @@
     <t>Request.priority</t>
   </si>
   <si>
+    <t>TQ1.9, RF1-2</t>
+  </si>
+  <si>
     <t>.priorityCode</t>
   </si>
   <si>
     <t>FiveWs.grade</t>
   </si>
   <si>
-    <t>MedicationRequest.doNotPerform</t>
+    <t>ServiceRequest.doNotPerform</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>True if request is prohibiting action</t>
-  </si>
-  <si>
-    <t>If true indicates that the provider is asking for the medication request not to occur.</t>
-  </si>
-  <si>
-    <t>If do not perform is not specified, the request is a positive request e.g. "do perform".</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.actionNegationInd</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reported[x]</t>
-  </si>
-  <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
-  </si>
-  <si>
-    <t>Reported rather than primary record</t>
-  </si>
-  <si>
-    <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=INF].role</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Reference(Medication)</t>
-  </si>
-  <si>
-    <t>Medication to be taken</t>
-  </si>
-  <si>
-    <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
-  </si>
-  <si>
-    <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>True if service/procedure should not be performed</t>
+  </si>
+  <si>
+    <t>Set this to true if the record is saying that the service/procedure should NOT be performed.</t>
+  </si>
+  <si>
+    <t>In general, only the code and timeframe will be present, though occasional additional qualifiers such as body site or even performer could be included to narrow the scope of the prohibition.  If the ServiceRequest.code and ServiceRequest.doNotPerform both contain negation, that will reinforce prohibition and should not have a double negative interpretation.</t>
+  </si>
+  <si>
+    <t>Used for do not ambulate, do not elevate head of bed, do not flush NG tube, do not take blood pressure on a certain arm, etc.</t>
+  </si>
+  <si>
+    <t>If missing, the request is a positive request e.g. "do perform"</t>
+  </si>
+  <si>
+    <t>Request.doNotPerform</t>
+  </si>
+  <si>
+    <t>.actionNegationInd</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service requested
+</t>
+  </si>
+  <si>
+    <t>What is being requested/ordered</t>
+  </si>
+  <si>
+    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+  </si>
+  <si>
+    <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
+  </si>
+  <si>
+    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred].</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
     <t>Request.code</t>
   </si>
   <si>
-    <t>Message/Body/NewRx/MedicationPrescribed--Medication.code.coding.code = Message/Body/NewRx/MedicationPrescribed/DrugCoded/ProductCode--Medication.code.coding.system = Message/Body/NewRx/MedicationPrescribed/DrugCoded/ProductCodeQualifier--Medication.code.coding.display = Message/Body/NewRx/MedicationPrescribed/DrugDescription</t>
-  </si>
-  <si>
-    <t>consumable.administrableMedication</t>
+    <t>PR1-3 / OBR-4  (varies by domain)</t>
+  </si>
+  <si>
+    <t>.code</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
   </si>
   <si>
-    <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.subject</t>
+    <t>Procedure.procedureCode</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">detailed instructions
+</t>
+  </si>
+  <si>
+    <t>Additional order information</t>
+  </si>
+  <si>
+    <t>Additional details and instructions about the how the services are to be delivered.   For example, and order for a urinary catheter may have an order detail for an external or indwelling catheter, or an order for a bandage may require additional instructions specifying how the bandage should be applied.</t>
+  </si>
+  <si>
+    <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
+  </si>
+  <si>
+    <t>Codified order entry details which are based on order context.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prr-1
+</t>
+  </si>
+  <si>
+    <t>NTE</t>
+  </si>
+  <si>
+    <t>ServiceRequest.quantity[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+RatioRange</t>
+  </si>
+  <si>
+    <t>Service amount</t>
+  </si>
+  <si>
+    <t>An amount of service being requested which can be a quantity ( for example $1,500 home modification), a ratio ( for example, 20 half day visits per month), or a range (2.0 to 1.8 Gy per fraction).</t>
+  </si>
+  <si>
+    <t>When ordering a service the number of service items may need to be specified separately from the the service item.</t>
+  </si>
+  <si>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>ServiceRequest.subject</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
-    <t>Who or group medication request is for</t>
-  </si>
-  <si>
-    <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
-  </si>
-  <si>
-    <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
+    <t>Individual or Entity the service is ordered for</t>
+  </si>
+  <si>
+    <t>On whom or what the service is to be performed. This is usually a human patient, but can also be requested on animals, groups of humans or animals, devices such as dialysis machines, or even locations (typically for environmental scans).</t>
   </si>
   <si>
     <t>Request.subject</t>
   </si>
   <si>
-    <t>Message/Body/NewRx/Patient--(need detail to link to specific patient … Patient.Identification in SCRIPT)</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
+    <t>PID</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
   </si>
   <si>
-    <t>PID-3-Patient ID List</t>
-  </si>
-  <si>
-    <t>MedicationRequest.encounter</t>
+    <t>ClinicalStatement.subject</t>
+  </si>
+  <si>
+    <t>ServiceRequest.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">context
+</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>Encounter created as part of encounter/admission/stay</t>
-  </si>
-  <si>
-    <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter."    If there is a need to link to episodes of care they will be handled with an extension.</t>
-  </si>
-  <si>
-    <t>Request.context</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN, code="type of encounter or episode"]</t>
+    <t>Encounter in which the request was created</t>
+  </si>
+  <si>
+    <t>An encounter that provides additional information about the healthcare context in which this request is made.</t>
+  </si>
+  <si>
+    <t>Request.encounter</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
   </si>
   <si>
     <t>FiveWs.context</t>
   </si>
   <si>
-    <t>PV1-19-Visit Number</t>
-  </si>
-  <si>
-    <t>MedicationRequest.supportingInformation</t>
+    <t>ClinicalStatement.encounter</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schedule
+</t>
+  </si>
+  <si>
+    <t>dateTime
+PeriodTiming</t>
+  </si>
+  <si>
+    <t>When service should occur</t>
+  </si>
+  <si>
+    <t>The date/time at which the requested service should occur.</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>TQ1/TQ2, OBR-7/OBR-8</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
+    <t>Procedure.procedureSchedule</t>
+  </si>
+  <si>
+    <t>ServiceRequest.asNeeded[x]</t>
+  </si>
+  <si>
+    <t>boolean
+CodeableConcept</t>
+  </si>
+  <si>
+    <t>Preconditions for service</t>
+  </si>
+  <si>
+    <t>If a CodeableConcept is present, it indicates the pre-condition for performing the service.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+  </si>
+  <si>
+    <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
+  </si>
+  <si>
+    <t>Proposal.prnReason.reason</t>
+  </si>
+  <si>
+    <t>ServiceRequest.authoredOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orderedOn
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date request signed</t>
+  </si>
+  <si>
+    <t>When the request transitioned to being actionable.</t>
+  </si>
+  <si>
+    <t>Request.authoredOn</t>
+  </si>
+  <si>
+    <t>ORC.9,  RF1-7 / RF1-9</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Proposal.proposedAtTime</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester</t>
+  </si>
+  <si>
+    <t>author
+orderer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+</t>
+  </si>
+  <si>
+    <t>Who/what is requesting service</t>
+  </si>
+  <si>
+    <t>The individual who initiated the request and has responsibility for its activation.</t>
+  </si>
+  <si>
+    <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
+  </si>
+  <si>
+    <t>Request.requester</t>
+  </si>
+  <si>
+    <t>ORC.12, PRT</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.statementAuthor</t>
+  </si>
+  <si>
+    <t>ServiceRequest.performerType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">specialty
+</t>
+  </si>
+  <si>
+    <t>Performer role</t>
+  </si>
+  <si>
+    <t>Desired type of performer for doing the requested service.</t>
+  </si>
+  <si>
+    <t>This is a  role, not  a participation type.  In other words, does not describe the task but describes the capacity.  For example, “compounding pharmacy”, “psychiatrist” or “internal referral”.</t>
+  </si>
+  <si>
+    <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+  </si>
+  <si>
+    <t>Request.performerType</t>
+  </si>
+  <si>
+    <t>PRT, RF!-3</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role[scoper.determinerCode=KIND].code</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>ServiceRequest.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">request recipient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Requested performer</t>
+  </si>
+  <si>
+    <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
+  </si>
+  <si>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+  </si>
+  <si>
+    <t>Request.performer</t>
+  </si>
+  <si>
+    <t>PRT, Practitioner: PRD-2/PRD-7 where PRD-3 = RT; Organization: PRD-10 where PRD-3 = RT</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.locationCode</t>
+  </si>
+  <si>
+    <t>Requested location</t>
+  </si>
+  <si>
+    <t>The preferred location(s) where the procedure should actually happen in coded or free text form. E.g. at home or nursing day care center.</t>
+  </si>
+  <si>
+    <t>A location type where services are delivered.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.locationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>A reference to the the preferred location(s) where the procedure should actually happen. E.g. at home or nursing day care center.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.reasonCode</t>
+  </si>
+  <si>
+    <t>Explanation/Justification for procedure or service</t>
+  </si>
+  <si>
+    <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
+  </si>
+  <si>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+  </si>
+  <si>
+    <t>Request.reasonCode</t>
+  </si>
+  <si>
+    <t>ORC.16, RF1-10</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+</t>
+  </si>
+  <si>
+    <t>Explanation/Justification for service or service</t>
+  </si>
+  <si>
+    <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
+  </si>
+  <si>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](http://hl7.org/fhir/R4/servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>Request.reasonReference</t>
+  </si>
+  <si>
+    <t>ORC.16</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+</t>
+  </si>
+  <si>
+    <t>Associated insurance coverage</t>
+  </si>
+  <si>
+    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be needed for delivering the requested service.</t>
+  </si>
+  <si>
+    <t>Request.insurance</t>
+  </si>
+  <si>
+    <t>IN1/IN2</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COVBY].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.supportingInfo</t>
+  </si>
+  <si>
+    <t>Ask at order entry question
+AOE</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
-    <t>Information to support ordering of the medication</t>
-  </si>
-  <si>
-    <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
+    <t>Additional clinical information</t>
+  </si>
+  <si>
+    <t>Additional clinical information about the patient or specimen that may influence the services or their interpretations.     This information includes diagnosis, clinical findings and other observations.  In laboratory ordering these are typically referred to as "ask at order entry questions (AOEs)".  This includes observations explicitly requested by the producer (filler) to provide context or supporting information needed to complete the order. For example,  reporting the amount of inspired oxygen for blood gas measurements.</t>
+  </si>
+  <si>
+    <t>To represent information about how the services are to be delivered use the `instructions` element.</t>
   </si>
   <si>
     <t>Request.supportingInfo</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=PERT].target[A_SupportingClinicalStatement CMET minimal with many different choices of classCodes(ORG, ENC, PROC, SPLY, SBADM, OBS) and each of the act class codes draws from one or more of the following moodCodes (EVN, DEF, INT PRMS, RQO, PRP, APT, ARQ, GOL)]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.authoredOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Accompanying segments</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=PERT].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
-    <t>When request was initially authored</t>
-  </si>
-  <si>
-    <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
-  </si>
-  <si>
-    <t>Request.authoredOn</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/WrittenDate</t>
-  </si>
-  <si>
-    <t>author.time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>RXE-32-Original Order Date/Time / ORC-9-Date/Time of Transaction</t>
-  </si>
-  <si>
-    <t>MedicationRequest.requester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t>Procedure Samples</t>
+  </si>
+  <si>
+    <t>One or more specimens that the laboratory procedure will use.</t>
+  </si>
+  <si>
+    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
+  </si>
+  <si>
+    <t>SPM</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SPC].role</t>
+  </si>
+  <si>
+    <t>ServiceRequest.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location
 </t>
   </si>
   <si>
-    <t>Who/What requested the Request</t>
-  </si>
-  <si>
-    <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>MedicationRequest.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson|CareTeam)
-</t>
-  </si>
-  <si>
-    <t>Intended performer of administration</t>
-  </si>
-  <si>
-    <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
-  </si>
-  <si>
-    <t>Request.performer</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>MedicationRequest.performerType</t>
-  </si>
-  <si>
-    <t>Desired kind of performer of the medication administration</t>
-  </si>
-  <si>
-    <t>Indicates the type of performer of the administration of the medication.</t>
-  </si>
-  <si>
-    <t>If specified without indicating a performer, this indicates that the performer must be of the specified type. If specified with a performer then it indicates the requirements of the performer if the designated performer is not available.</t>
-  </si>
-  <si>
-    <t>Identifies the type of individual that is desired to administer the medication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
-  </si>
-  <si>
-    <t>Request.performerType</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role[scoper.determinerCode=KIND].code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.recorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
-</t>
-  </si>
-  <si>
-    <t>Person who entered the request</t>
-  </si>
-  <si>
-    <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=TRANS].role[classCode=ASSIGNED].code (HealthcareProviderType)</t>
-  </si>
-  <si>
-    <t>FiveWs.who</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode</t>
-  </si>
-  <si>
-    <t>Reason or indication for ordering or not ordering the medication</t>
-  </si>
-  <si>
-    <t>The reason or the indication for ordering or not ordering the medication.</t>
-  </si>
-  <si>
-    <t>This could be a diagnosis code. If a full condition record exists or additional detail is needed, use reasonReference.</t>
-  </si>
-  <si>
-    <t>A coded concept indicating why the medication was ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Diagnosis/Primary/Value</t>
-  </si>
-  <si>
-    <t>reason.observation.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ORC-16-Order Control Code Reason /RXE-27-Give Indication/RXO-20-Indication / RXD-21-Indication / RXG-22-Indication / RXA-19-Indication</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|Observation)
-</t>
-  </si>
-  <si>
-    <t>Condition or observation that supports why the prescription is being written</t>
-  </si>
-  <si>
-    <t>Condition or observation that supports why the medication was ordered.</t>
-  </si>
-  <si>
-    <t>This is a reference to a condition or observation that is the reason for the medication order.  If only a code exists, use reasonCode.</t>
-  </si>
-  <si>
-    <t>Request.reasonReference</t>
-  </si>
-  <si>
-    <t>reason.observation[code=ASSERTION].value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical
-</t>
-  </si>
-  <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
-  </si>
-  <si>
-    <t>Request.instantiates</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>MedicationRequest.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
-</t>
-  </si>
-  <si>
-    <t>What request fulfills</t>
-  </si>
-  <si>
-    <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
-  </si>
-  <si>
-    <t>Request.basedOn</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target[classCode=SBADM or PROC or PCPR or OBS, moodCode=RQO orPLAN or PRP]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.groupIdentifier</t>
-  </si>
-  <si>
-    <t>Composite request this is part of</t>
-  </si>
-  <si>
-    <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
-  </si>
-  <si>
-    <t>Requests are linked either by a "basedOn" relationship (i.e. one request is fulfilling another) or by having a common requisition. Requests that are part of the same requisition are generally treated independently from the perspective of changing their state or maintaining them after initial creation.</t>
-  </si>
-  <si>
-    <t>Request.groupIdentifier</t>
-  </si>
-  <si>
-    <t>.outboundRelationship(typeCode=COMP].target[classCode=SBADM, moodCode=INT].id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.courseOfTherapyType</t>
-  </si>
-  <si>
-    <t>Overall pattern of medication administration</t>
-  </si>
-  <si>
-    <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
-  </si>
-  <si>
-    <t>This attribute should not be confused with the protocol of the medication.</t>
-  </si>
-  <si>
-    <t>Identifies the overall pattern of medication administratio.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
-  </si>
-  <si>
-    <t>Act.code where classCode = LIST and moodCode = EVN</t>
-  </si>
-  <si>
-    <t>MedicationRequest.insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
-</t>
-  </si>
-  <si>
-    <t>Associated insurance coverage</t>
-  </si>
-  <si>
-    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be required for delivering the requested service.</t>
-  </si>
-  <si>
-    <t>Request.insurance</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COVBY].target</t>
-  </si>
-  <si>
-    <t>MedicationRequest.note</t>
+    <t>Location on Body</t>
+  </si>
+  <si>
+    <t>Anatomic location where the procedure should be performed. This is the target site.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
+  </si>
+  <si>
+    <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>Procedure.targetBodySite</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note</t>
   </si>
   <si>
     <t xml:space="preserve">Annotation
 </t>
   </si>
   <si>
-    <t>Information about the prescription</t>
-  </si>
-  <si>
-    <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
+    <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
     <t>Request.note</t>
   </si>
   <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Note</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=OBS,moodCode=EVN,code="annotation"].value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage
-</t>
-  </si>
-  <si>
-    <t>How the medication should be taken</t>
-  </si>
-  <si>
-    <t>Indicates how the medication is to be used by the patient.</t>
-  </si>
-  <si>
-    <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>see dosageInstruction mapping</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Medication supply authorization</t>
-  </si>
-  <si>
-    <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/ExpirationDate</t>
-  </si>
-  <si>
-    <t>component.supplyEvent</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.id</t>
+    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=ANNGEN, moodCode=EVN].value[xsi:type=ST]</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.additionalText</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill</t>
-  </si>
-  <si>
-    <t>First fill details</t>
-  </si>
-  <si>
-    <t>Indicates the quantity or duration for the first dispense of the medication.</t>
-  </si>
-  <si>
-    <t>If populating this element, either the quantity or the duration must be included.</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration -&gt; ActRelationship[sequenceNumber = '1'] -&gt; Supply</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.modifierExtension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
-</t>
-  </si>
-  <si>
-    <t>First fill quantity</t>
-  </si>
-  <si>
-    <t>The amount or quantity to provide as part of the first dispense.</t>
-  </si>
-  <si>
-    <t>Supply.quantity[moodCode=RQO]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration
-</t>
-  </si>
-  <si>
-    <t>First fill duration</t>
-  </si>
-  <si>
-    <t>The length of time that the first dispense is expected to last.</t>
-  </si>
-  <si>
-    <t>Supply.effectivetime[moodCode=RQO]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.dispenseInterval</t>
-  </si>
-  <si>
-    <t>Minimum period of time between dispenses</t>
-  </si>
-  <si>
-    <t>The minimum period of time that must occur between dispenses of the medication.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.validityPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period supply is authorized for</t>
-  </si>
-  <si>
-    <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
-  </si>
-  <si>
-    <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
-  </si>
-  <si>
-    <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Refills</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.numberOfRepeatsAllowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsignedInt
-</t>
-  </si>
-  <si>
-    <t>Number of refills authorized</t>
-  </si>
-  <si>
-    <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
-  </si>
-  <si>
-    <t>If displaying "number of authorized fills", add 1 to this number.</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>
-  </si>
-  <si>
-    <t>repeatNumber</t>
-  </si>
-  <si>
-    <t>RXE-12-Number of Refills</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.quantity</t>
-  </si>
-  <si>
-    <t>Amount of medication to supply per dispense</t>
-  </si>
-  <si>
-    <t>The amount that is to be dispensed for one fill.</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
-  </si>
-  <si>
-    <t>Number of days supply per dispense</t>
-  </si>
-  <si>
-    <t>Identifies the period time over which the supplied product is expected to be used, or the length of time the dispense is expected to last.</t>
-  </si>
-  <si>
-    <t>In some situations, this attribute may be used instead of quantity to identify the amount supplied by how long it is expected to last, rather than the physical quantity issued, e.g. 90 days supply of medication (based on an ordered dosage). When possible, it is always better to specify quantity, as this tends to be more precise. expectedSupplyDuration will always be an estimate that can be influenced by external factors.</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
-  </si>
-  <si>
-    <t>expectedUseTime</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Intended dispenser</t>
-  </si>
-  <si>
-    <t>Indicates the intended dispensing Organization specified by the prescriber.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SPLY, moodCode=RQO] .participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.substitution</t>
-  </si>
-  <si>
-    <t>Any restrictions on medication substitution</t>
-  </si>
-  <si>
-    <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
-  </si>
-  <si>
-    <t>specific values within Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
-  </si>
-  <si>
-    <t>subjectOf.substitutionPersmission</t>
-  </si>
-  <si>
-    <t>MedicationRequest.substitution.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.substitution.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.substitution.modifierExtension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.substitution.allowed[x]</t>
-  </si>
-  <si>
-    <t>boolean
-CodeableConcept</t>
-  </si>
-  <si>
-    <t>Whether substitution is allowed or not</t>
-  </si>
-  <si>
-    <t>True if the prescriber allows a different drug to be dispensed from what was prescribed.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because whether substitution is allow or not, it cannot be ignored.</t>
-  </si>
-  <si>
-    <t>Identifies the type of substitution allowed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>RXO-9-Allow Substitutions / RXE-9-Substitution Status</t>
-  </si>
-  <si>
-    <t>MedicationRequest.substitution.reason</t>
-  </si>
-  <si>
-    <t>Why should (not) substitution be made</t>
-  </si>
-  <si>
-    <t>Indicates the reason for the substitution, or why substitution must or must not be performed.</t>
-  </si>
-  <si>
-    <t>A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
-  </si>
-  <si>
-    <t>not mapped</t>
-  </si>
-  <si>
-    <t>reasonCode</t>
-  </si>
-  <si>
-    <t>RXE-9 Substition status</t>
-  </si>
-  <si>
-    <t>MedicationRequest.priorPrescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
-</t>
-  </si>
-  <si>
-    <t>An order/prescription that is being replaced</t>
-  </si>
-  <si>
-    <t>A link to a resource representing an earlier order related order or prescription.</t>
-  </si>
-  <si>
-    <t>Request.replaces</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=?RPLC or ?SUCC]/target[classCode=SBADM,moodCode=RQO]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.detectedIssue</t>
-  </si>
-  <si>
-    <t>Contraindication
-Drug Utilization Review (DUR)Alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
-</t>
-  </si>
-  <si>
-    <t>Clinical Issue with action</t>
-  </si>
-  <si>
-    <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
-  </si>
-  <si>
-    <t>This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=ALRT,moodCode=EVN].value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.eventHistory</t>
+    <t>Patient or consumer-oriented instructions</t>
+  </si>
+  <si>
+    <t>Instructions in terms that are understood by the patient or consumer.</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
-    <t>A list of events of interest in the lifecycle</t>
-  </si>
-  <si>
-    <t>Links to Provenance records for past versions of this resource or fulfilling request or event resources that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the resource.</t>
-  </si>
-  <si>
-    <t>This might not include provenances for all versions of the request – only those deemed “relevant” or important. This SHALL NOT include the provenance associated with this current version of the resource. (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update. Until then, it can be queried directly as the provenance that points to this version using _revinclude All Provenances should have some historical version of this Request as their subject.).</t>
+    <t>Request provenance</t>
+  </si>
+  <si>
+    <t>Key events in the history of the request.</t>
+  </si>
+  <si>
+    <t>This might not include provenances for all versions of the request – only those deemed “relevant” or important.+This SHALL NOT include the Provenance associated with this current version of the resource.  (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update.  Until then, it can be queried directly as the Provenance that points to this version using _revinclude+All Provenances should have some historical version of this Request as their subject.</t>
   </si>
   <si>
     <t>Request.relevantHistory</t>
@@ -1808,20 +1722,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.28515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="60.28515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="41.13671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.71484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.99609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1835,22 +1749,22 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="161.5859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="186.83203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="85.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="163.4453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="66.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2802,7 +2716,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2821,17 +2735,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -2868,16 +2780,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -2901,7 +2811,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -2915,43 +2825,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -2999,7 +2907,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3008,7 +2916,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3020,7 +2928,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -3031,12 +2939,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3045,7 +2955,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
@@ -3057,17 +2967,15 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3116,7 +3024,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3125,66 +3033,66 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3209,13 +3117,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3233,31 +3141,31 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3265,44 +3173,46 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3326,13 +3236,13 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
@@ -3350,28 +3260,28 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3382,10 +3292,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3393,31 +3303,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3428,7 +3338,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3443,13 +3353,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3467,13 +3377,13 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
@@ -3482,27 +3392,27 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3522,19 +3432,19 @@
         <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3560,13 +3470,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3584,7 +3494,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3599,16 +3509,16 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -3616,10 +3526,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3630,7 +3540,7 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3642,15 +3552,17 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3675,13 +3587,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3699,13 +3611,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3714,16 +3626,16 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -3731,43 +3643,41 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3816,13 +3726,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3831,13 +3741,13 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
@@ -3848,21 +3758,21 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3874,13 +3784,13 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3931,13 +3841,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3946,13 +3856,13 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
@@ -3963,18 +3873,18 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -3989,18 +3899,20 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4024,13 +3936,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4048,10 +3960,10 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -4063,27 +3975,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4100,22 +4012,22 @@
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4141,13 +4053,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4165,7 +4077,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4180,27 +4092,27 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4208,7 +4120,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4217,22 +4129,22 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>239</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4243,7 +4155,7 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>82</v>
@@ -4258,13 +4170,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4282,10 +4194,10 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4297,27 +4209,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4337,19 +4249,23 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4373,13 +4289,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4397,7 +4313,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4412,16 +4328,16 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4429,10 +4345,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4455,20 +4371,22 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q23" s="2"/>
+      <c r="Q23" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="R23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4488,13 +4406,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4512,7 +4430,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4527,27 +4445,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4564,26 +4482,32 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4627,7 +4551,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4642,16 +4566,16 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4659,14 +4583,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4682,18 +4606,20 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4718,13 +4644,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4742,7 +4668,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4757,19 +4683,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="26">
@@ -4781,14 +4707,14 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4800,16 +4726,16 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4835,13 +4761,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4865,36 +4791,36 @@
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4914,19 +4840,21 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4974,7 +4902,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4992,13 +4920,13 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5006,10 +4934,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5017,10 +4945,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5029,20 +4957,18 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5067,13 +4993,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5091,13 +5017,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5106,38 +5032,38 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5146,7 +5072,7 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>301</v>
@@ -5157,9 +5083,7 @@
       <c r="M29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5208,13 +5132,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5223,38 +5147,38 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5266,13 +5190,13 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5323,13 +5247,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5338,27 +5262,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5369,7 +5293,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5381,13 +5305,13 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>320</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5414,13 +5338,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5438,13 +5362,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5459,32 +5383,32 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5496,13 +5420,13 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5553,13 +5477,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5568,31 +5492,31 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5611,18 +5535,18 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>149</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5670,7 +5594,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5685,31 +5609,31 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5725,19 +5649,19 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5763,13 +5687,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5787,7 +5711,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5802,16 +5726,16 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5819,14 +5743,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5842,18 +5766,20 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5902,7 +5828,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5917,16 +5843,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5934,10 +5860,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5957,16 +5883,16 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>234</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5993,13 +5919,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6017,7 +5943,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6032,16 +5958,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6049,10 +5975,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6072,20 +5998,18 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6134,7 +6058,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6149,16 +6073,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6166,10 +6090,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6180,7 +6104,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6189,18 +6113,20 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>356</v>
+        <v>234</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6225,13 +6151,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6249,13 +6175,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6264,16 +6190,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6281,10 +6207,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6295,7 +6221,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6304,18 +6230,20 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6364,31 +6292,31 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6396,14 +6324,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6422,17 +6350,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>397</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>138</v>
+        <v>398</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6481,7 +6407,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6493,16 +6419,16 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6513,14 +6439,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6533,26 +6459,24 @@
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>405</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6600,7 +6524,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6612,16 +6536,16 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>134</v>
+        <v>411</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6632,10 +6556,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6646,7 +6570,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6655,19 +6579,19 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6717,13 +6641,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6735,10 +6659,10 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6749,21 +6673,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6772,19 +6696,23 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>362</v>
+        <v>234</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6808,13 +6736,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -6832,46 +6760,46 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>365</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>366</v>
+        <v>427</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>381</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>381</v>
+        <v>429</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6890,17 +6818,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -6949,7 +6875,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6961,66 +6887,62 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>366</v>
+        <v>433</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>436</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7068,28 +6990,28 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>134</v>
+        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7100,10 +7022,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7114,7 +7036,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7126,15 +7048,17 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7183,13 +7107,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7198,1878 +7122,18 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>387</v>
+        <v>446</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -459,46 +459,23 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ServiceRequest.extension:cpg-rating</t>
-  </si>
-  <si>
-    <t>cpg-rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-rating}
+    <t>ServiceRequest.extension:structured-rating</t>
+  </si>
+  <si>
+    <t>structured-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
 </t>
   </si>
   <si>
-    <t>CPG Rating Extension</t>
+    <t>PSS Rating Extension</t>
   </si>
   <si>
     <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.extension:coded-rating</t>
-  </si>
-  <si>
-    <t>coded-rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSCodedRating}
-</t>
-  </si>
-  <si>
-    <t>PSS Rating Extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.extension:structured-rating</t>
-  </si>
-  <si>
-    <t>structured-rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
 </t>
   </si>
   <si>
@@ -1722,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO46"/>
+  <dimension ref="A1:AO44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.13671875" customWidth="true" bestFit="true"/>
@@ -2838,7 +2815,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
@@ -2942,41 +2919,43 @@
         <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3024,7 +3003,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3033,7 +3012,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>142</v>
@@ -3045,7 +3024,7 @@
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>82</v>
@@ -3056,14 +3035,12 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3081,18 +3058,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3141,7 +3120,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3150,37 +3129,37 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3193,26 +3172,24 @@
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J13" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3260,7 +3237,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3272,16 +3249,16 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3292,10 +3269,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3318,16 +3295,16 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3377,7 +3354,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3392,31 +3369,31 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3435,17 +3412,15 @@
         <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3494,7 +3469,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3509,13 +3484,13 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -3526,14 +3501,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3552,17 +3527,15 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3611,7 +3584,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3626,13 +3599,13 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
@@ -3643,21 +3616,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3669,16 +3642,20 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -3726,13 +3703,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3741,13 +3718,13 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
@@ -3758,41 +3735,43 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -3817,13 +3796,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -3841,13 +3820,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3856,35 +3835,35 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -3893,26 +3872,24 @@
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -3921,7 +3898,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -3936,13 +3913,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -3960,10 +3937,10 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -3975,16 +3952,16 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -3992,10 +3969,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4003,33 +3980,35 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4053,13 +4032,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4077,13 +4056,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4092,27 +4071,27 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4120,7 +4099,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4129,7 +4108,7 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>92</v>
@@ -4138,24 +4117,24 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>82</v>
@@ -4170,13 +4149,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4194,10 +4173,10 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4209,16 +4188,16 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4226,10 +4205,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4240,36 +4219,38 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="R22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4289,13 +4270,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4313,13 +4294,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4328,16 +4309,16 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4345,14 +4326,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4371,22 +4352,22 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>111</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4406,13 +4387,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4430,7 +4411,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4445,69 +4426,65 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q24" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4527,13 +4504,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4551,46 +4528,46 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4609,18 +4586,18 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4644,13 +4621,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4668,7 +4645,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4683,38 +4660,38 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4726,17 +4703,15 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4761,13 +4736,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4785,46 +4760,46 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>274</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4843,18 +4818,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4902,7 +4875,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4917,35 +4890,35 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -4960,13 +4933,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5017,10 +4990,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>91</v>
@@ -5032,31 +5005,31 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>298</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5075,13 +5048,13 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5108,13 +5081,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5132,7 +5105,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5147,31 +5120,31 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5190,13 +5163,13 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5247,7 +5220,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5262,31 +5235,31 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5305,15 +5278,17 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5338,13 +5313,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5362,7 +5337,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5377,31 +5352,31 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5420,15 +5395,17 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5453,13 +5430,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5477,7 +5454,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5492,38 +5469,38 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5535,16 +5512,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5594,13 +5571,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -5609,38 +5586,38 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5652,17 +5629,15 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5687,13 +5662,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5711,13 +5686,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -5726,16 +5701,16 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5743,14 +5718,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5769,17 +5744,15 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>362</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5828,7 +5801,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5843,16 +5816,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5860,10 +5833,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5886,15 +5859,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -5919,31 +5894,31 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5958,16 +5933,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -5975,10 +5950,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6001,15 +5976,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6058,7 +6035,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6073,16 +6050,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6090,10 +6067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6113,20 +6090,18 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>234</v>
+        <v>390</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6151,13 +6126,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6175,7 +6150,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6190,16 +6165,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6207,14 +6182,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6230,19 +6205,19 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6292,7 +6267,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6307,16 +6282,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6324,10 +6299,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6347,18 +6322,20 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6407,7 +6384,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6422,13 +6399,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6439,14 +6416,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6462,21 +6439,23 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>405</v>
+        <v>227</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6500,13 +6479,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6524,7 +6503,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6539,27 +6518,27 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>410</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6579,20 +6558,18 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>414</v>
+        <v>51</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6641,7 +6618,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6656,38 +6633,38 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>417</v>
+        <v>276</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6699,20 +6676,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>234</v>
+        <v>429</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6736,13 +6709,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -6760,13 +6733,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6778,24 +6751,24 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>276</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6818,15 +6791,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>51</v>
+        <v>435</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -6875,7 +6850,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6890,250 +6865,18 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -435,21 +435,21 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -459,31 +459,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ServiceRequest.extension:structured-rating</t>
-  </si>
-  <si>
-    <t>structured-rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
-</t>
-  </si>
-  <si>
-    <t>PSS Rating Extension</t>
-  </si>
-  <si>
-    <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ServiceRequest.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -491,9 +467,6 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -1699,12 +1672,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO44"/>
+  <dimension ref="A1:AO43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.13671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.71484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.71484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2693,7 +2666,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2712,15 +2685,17 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -2757,14 +2732,16 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -2788,7 +2765,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -2802,13 +2779,11 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2821,22 +2796,26 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -2884,7 +2863,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2893,7 +2872,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -2905,7 +2884,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -2916,14 +2895,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2936,26 +2915,24 @@
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3003,7 +2980,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3015,30 +2992,30 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3061,16 +3038,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3120,7 +3097,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3135,19 +3112,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -3178,16 +3155,16 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3252,13 +3229,13 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3269,14 +3246,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3295,17 +3272,15 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3354,7 +3329,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3369,13 +3344,13 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -3515,7 +3490,7 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3527,16 +3502,20 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="O16" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3590,7 +3569,7 @@
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3599,13 +3578,13 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
@@ -3616,18 +3595,18 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -3636,13 +3615,13 @@
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>197</v>
@@ -3653,9 +3632,7 @@
       <c r="N17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="O17" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -3679,13 +3656,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3703,10 +3680,10 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>91</v>
@@ -3718,27 +3695,27 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3764,13 +3741,13 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3781,7 +3758,7 @@
         <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>82</v>
@@ -3796,31 +3773,31 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>91</v>
@@ -3835,27 +3812,27 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3863,33 +3840,35 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -3898,7 +3877,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -3913,13 +3892,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -3937,13 +3916,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -3952,16 +3931,16 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -3969,10 +3948,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3983,7 +3962,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -3995,24 +3974,22 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O20" t="s" s="2">
         <v>231</v>
       </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q20" s="2"/>
+      <c r="Q20" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="R20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4032,7 +4009,7 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="Y20" t="s" s="2">
         <v>233</v>
@@ -4056,13 +4033,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4071,16 +4048,16 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4088,10 +4065,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4108,72 +4085,76 @@
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4188,16 +4169,16 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4205,14 +4186,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4225,76 +4206,72 @@
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q22" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="R22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4309,38 +4286,38 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4352,16 +4329,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4387,13 +4364,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4411,53 +4388,53 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4469,18 +4446,18 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="O24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4504,13 +4481,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4528,16 +4505,16 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
@@ -4546,24 +4523,24 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4571,7 +4548,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
@@ -4586,18 +4563,16 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4645,10 +4620,10 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>91</v>
@@ -4660,35 +4635,35 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -4703,13 +4678,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4760,10 +4735,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>91</v>
@@ -4775,31 +4750,31 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4818,13 +4793,13 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4875,7 +4850,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4890,31 +4865,31 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4933,13 +4908,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4966,13 +4941,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -4990,7 +4965,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5005,16 +4980,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>311</v>
@@ -5029,7 +5004,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5048,13 +5023,13 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5081,13 +5056,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5120,31 +5095,31 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5163,15 +5138,17 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5220,7 +5197,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5235,31 +5212,31 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5278,16 +5255,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>332</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5313,13 +5290,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5337,7 +5314,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5352,38 +5329,38 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5395,16 +5372,16 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>227</v>
+        <v>346</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5430,13 +5407,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5454,13 +5431,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5469,16 +5446,16 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5486,14 +5463,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5512,17 +5489,15 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>357</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5547,13 +5522,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5571,7 +5546,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5586,16 +5561,16 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>360</v>
-      </c>
       <c r="AN33" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5603,10 +5578,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5629,13 +5604,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5662,13 +5637,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5686,7 +5661,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5707,10 +5682,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5718,10 +5693,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5744,15 +5719,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>368</v>
+        <v>219</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5777,13 +5754,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -5801,7 +5778,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5816,16 +5793,16 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5833,10 +5810,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5859,16 +5836,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5894,13 +5871,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -5918,7 +5895,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5933,16 +5910,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -5973,7 +5950,7 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>382</v>
@@ -5984,9 +5961,7 @@
       <c r="M37" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N37" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6050,16 +6025,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AN37" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6067,14 +6042,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6101,7 +6076,9 @@
       <c r="M38" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6150,7 +6127,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6165,13 +6142,13 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6182,14 +6159,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6205,7 +6182,7 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>398</v>
@@ -6267,7 +6244,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6282,13 +6259,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6299,14 +6276,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6325,18 +6302,20 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6360,13 +6339,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6384,7 +6363,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6402,28 +6381,28 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6439,23 +6418,19 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>227</v>
+        <v>415</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>414</v>
+        <v>51</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N41" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="O41" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6479,13 +6454,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6503,7 +6478,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6518,27 +6493,27 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>410</v>
+        <v>268</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6549,7 +6524,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6558,16 +6533,16 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6618,13 +6593,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6633,27 +6608,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6664,7 +6639,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6673,18 +6648,20 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6733,13 +6710,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6748,135 +6725,18 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseServiceRequest</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseServiceRequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
